--- a/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
+++ b/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
@@ -715,7 +715,7 @@
       <c r="C4" s="51" t="n"/>
       <c r="D4" s="52" t="n"/>
     </row>
-    <row r="5" ht="12.75" customFormat="1" customHeight="1" s="53">
+    <row r="5" ht="80" customFormat="1" customHeight="1" s="53">
       <c r="B5" s="54" t="inlineStr">
         <is>
           <t>Student Details</t>
@@ -728,11 +728,15 @@
       </c>
       <c r="D5" s="56" t="inlineStr">
         <is>
-          <t>[Your name]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="12.75" customFormat="1" customHeight="1" s="53">
+          <t>Ali Jan
+Humaiz Khan
+Muhammad Ehtisham Shakeel
+Muhammad Waleed
+Ali Turab</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customFormat="1" customHeight="1" s="53">
       <c r="B6" s="57" t="n"/>
       <c r="C6" s="58" t="inlineStr">
         <is>
@@ -741,7 +745,11 @@
       </c>
       <c r="D6" s="59" t="inlineStr">
         <is>
-          <t>[Enrollment no.]</t>
+          <t>Student1661815
+Student1659420
+Student1657963
+Student1659932
+Student1667727</t>
         </is>
       </c>
     </row>
@@ -976,7 +984,7 @@
       </c>
       <c r="D26" s="85" t="inlineStr">
         <is>
-          <t>All requirements finished: public tracking, advanced search, plan change, order cancel, documents by year and city, theme and animations, test checklist, report and presentation.</t>
+          <t>All requirements finished: public tracking, advanced search, plan change, order cancel, documents by year and city, theme and animations, test checklist, report and presentation. Final interface: light / dark theme switch and original illustrations; user guide, report, presentation and demo video updated.</t>
         </is>
       </c>
     </row>

--- a/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
+++ b/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="D7" s="61" t="inlineStr">
         <is>
-          <t>[Curriculum]</t>
+          <t>ADSE</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" s="61" t="inlineStr">
         <is>
-          <t>[Semester]</t>
+          <t>Semester 3</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>[Centre name]</t>
+          <t>Aptech Center NN2</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="D14" s="72" t="inlineStr">
         <is>
-          <t>[DD/MMM/YYYY]</t>
+          <t>17/Oct/2026</t>
         </is>
       </c>
     </row>

--- a/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
+++ b/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="D7" s="61" t="inlineStr">
         <is>
-          <t>ADSE</t>
+          <t>ADSE (ACCP in AI)</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" s="61" t="inlineStr">
         <is>
-          <t>Semester 3</t>
+          <t>Term 3</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Aptech Center NN2</t>
+          <t>ACE-PK-Karachi-20-North Nazimabad-2</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="D12" s="70" t="inlineStr">
         <is>
-          <t>[Duration in days]</t>
+          <t>30 days</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D13" s="72" t="inlineStr">
         <is>
-          <t>[DD/MMM/YYYY]</t>
+          <t>17/Sep/2026</t>
         </is>
       </c>
     </row>

--- a/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
+++ b/documentation/Nexus_Documentation/Nexus_Status_Report.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="D17" s="72" t="inlineStr">
         <is>
-          <t>[DD/MMM/YYYY]</t>
+          <t>27/Sep/2026</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="D23" s="72" t="inlineStr">
         <is>
-          <t>[DD/MMM/YYYY]</t>
+          <t>07/Oct/2026</t>
         </is>
       </c>
     </row>
